--- a/report_forms/037_end_of_shift_incident_report--report_forms.xlsx
+++ b/report_forms/037_end_of_shift_incident_report--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'equipment_failure',_'value':_'equipment_failure'}</t>
+          <t>equipment_failure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'Equipment failure', 'value': 'Equipment failure'}</t>
+          <t>Equipment failure</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'employee_error',_'value':_'employee_error'}</t>
+          <t>employee_error</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'Employee error', 'value': 'Employee error'}</t>
+          <t>Employee error</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_103,_'label':_'weather',_'value':_'weather'}</t>
+          <t>weather</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 103, 'label': 'Weather', 'value': 'Weather'}</t>
+          <t>Weather</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_104,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 104, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_201,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 201, 'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_202,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 202, 'label': 'Jane', 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_203,_'label':_'jim',_'value':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 203, 'label': 'Jim', 'value': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_301,_'label':_true,_'value':_'reported'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 301, 'label': True, 'value': 'Reported'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_302,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 302, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
